--- a/PhIPSeq_Manifest_Template_v5.xlsx
+++ b/PhIPSeq_Manifest_Template_v5.xlsx
@@ -779,7 +779,7 @@
       </c>
       <c r="C6" s="34" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Subject age in years at collection. Whole number, 0-120.</t>
+          <t>Subject age in years at collection, 0-120. Decimals allowed, for infants and for ages recorded to part of a year.</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>serum, plasma, CSF, mAb, control or assay control. serum/plasma/CSF are placed by autofill; the rest are placed by hand in the control area.</t>
+          <t>serum, plasma, whole blood, CSF, mAb, control or assay control. serum, plasma, whole blood and CSF are placed by autofill; the rest are placed by hand in the control area.</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
@@ -3430,15 +3430,15 @@
     <dataValidation sqref="C3:C102" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="subject_id" error="subject_id is required: tiu_id is built from sample_id and subject_id, and the designer uses it to keep one subject's samples on one plate." type="custom">
       <formula1>=LEN(TRIM($C3))&gt;0</formula1>
     </dataValidation>
-    <dataValidation sqref="D3:D102" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="subject_age_yrs" error="Age must be a whole number of years between 0 and 120." type="whole" operator="between">
+    <dataValidation sqref="D3:D102" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="subject_age_yrs" error="Age in years, between 0 and 120. Decimals are allowed — use them for infants and for ages recorded to part of a year (e.g. 0.5)." type="decimal" operator="between">
       <formula1>0</formula1>
       <formula2>120</formula2>
     </dataValidation>
     <dataValidation sqref="E3:E102" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="subject_sex" error="Choose M, F or Unknown." type="list">
       <formula1>"M,F,Unknown"</formula1>
     </dataValidation>
-    <dataValidation sqref="G3:G102" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="sample_type" error="sample_type is required. serum, plasma and CSF are placed by autofill; mAb, control and assay control are placed by hand in the control area." type="list">
-      <formula1>"serum,plasma,CSF,mAb,control,assay control"</formula1>
+    <dataValidation sqref="G3:G102" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="sample_type" error="sample_type is required. serum, plasma, whole blood and CSF are placed by autofill; mAb, control and assay control are placed by hand in the control area." type="list">
+      <formula1>"serum,plasma,whole blood,CSF,mAb,control,assay control"</formula1>
     </dataValidation>
     <dataValidation sqref="H3:H102" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="volume_mL" error="Volume must be a positive number of millilitres (e.g. 0.5)." type="decimal" operator="greaterThan">
       <formula1>0</formula1>
